--- a/businesses/notion-sheets-trackers/products/Freelancer_Finance_Tracker_DEMO.xlsx
+++ b/businesses/notion-sheets-trackers/products/Freelancer_Finance_Tracker_DEMO.xlsx
@@ -24395,7 +24395,7 @@
         </is>
       </c>
       <c r="C11" s="15" t="n">
-        <v>72686</v>
+        <v>46293</v>
       </c>
       <c r="D11" s="16" t="n">
         <v>30</v>
